--- a/artfynd/A 35585-2025 artfynd.xlsx
+++ b/artfynd/A 35585-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128937276</v>
       </c>
       <c r="B2" t="n">
-        <v>98568</v>
+        <v>98573</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35585-2025 artfynd.xlsx
+++ b/artfynd/A 35585-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128937276</v>
       </c>
       <c r="B2" t="n">
-        <v>98573</v>
+        <v>98576</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35585-2025 artfynd.xlsx
+++ b/artfynd/A 35585-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128937276</v>
       </c>
       <c r="B2" t="n">
-        <v>98576</v>
+        <v>98586</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35585-2025 artfynd.xlsx
+++ b/artfynd/A 35585-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128937276</v>
       </c>
       <c r="B2" t="n">
-        <v>98586</v>
+        <v>98593</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35585-2025 artfynd.xlsx
+++ b/artfynd/A 35585-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128937276</v>
       </c>
       <c r="B2" t="n">
-        <v>98593</v>
+        <v>98595</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35585-2025 artfynd.xlsx
+++ b/artfynd/A 35585-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128937276</v>
       </c>
       <c r="B2" t="n">
-        <v>98595</v>
+        <v>98621</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35585-2025 artfynd.xlsx
+++ b/artfynd/A 35585-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128937276</v>
       </c>
       <c r="B2" t="n">
-        <v>98621</v>
+        <v>98622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35585-2025 artfynd.xlsx
+++ b/artfynd/A 35585-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128937276</v>
       </c>
       <c r="B2" t="n">
-        <v>98622</v>
+        <v>98623</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35585-2025 artfynd.xlsx
+++ b/artfynd/A 35585-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128937276</v>
       </c>
       <c r="B2" t="n">
-        <v>98623</v>
+        <v>98627</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35585-2025 artfynd.xlsx
+++ b/artfynd/A 35585-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128937276</v>
       </c>
       <c r="B2" t="n">
-        <v>98627</v>
+        <v>98629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35585-2025 artfynd.xlsx
+++ b/artfynd/A 35585-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128937276</v>
       </c>
       <c r="B2" t="n">
-        <v>98629</v>
+        <v>98633</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35585-2025 artfynd.xlsx
+++ b/artfynd/A 35585-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128937276</v>
       </c>
       <c r="B2" t="n">
-        <v>98633</v>
+        <v>98641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35585-2025 artfynd.xlsx
+++ b/artfynd/A 35585-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128937276</v>
+        <v>128937239</v>
       </c>
       <c r="B2" t="n">
-        <v>98641</v>
+        <v>8444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>335387</v>
+        <v>335200</v>
       </c>
       <c r="R2" t="n">
-        <v>6616579</v>
+        <v>6616532</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128937239</v>
+        <v>128937276</v>
       </c>
       <c r="B3" t="n">
-        <v>8439</v>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>335200</v>
+        <v>335387</v>
       </c>
       <c r="R3" t="n">
-        <v>6616532</v>
+        <v>6616579</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 35585-2025 artfynd.xlsx
+++ b/artfynd/A 35585-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128937239</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,8 +884,17 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128937276</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>